--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486480_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486480_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. LOBACO MUÑOZ</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8656</v>
+        <v>6.1684</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3911</v>
+        <v>3.0619</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4744</v>
+        <v>3.1066</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.7262</v>
+        <v>3.4977</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1461</v>
+        <v>0.3716</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5800999999999999</v>
+        <v>3.1261</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.0511</v>
+        <v>3.7258</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4047</v>
+        <v>0.6244</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4558</v>
+        <v>3.1014</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6751</v>
+        <v>-0.2281</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5508</v>
+        <v>-0.2528</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1243</v>
+        <v>0.0247</v>
       </c>
       <c r="P2" t="n">
-        <v>2.8276</v>
+        <v>0.2175</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R2" t="n">
-        <v>2.8276</v>
+        <v>3.4801</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6563</v>
+        <v>0.9103</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1823</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.526</v>
+        <v>0.0066</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1079</v>
+        <v>1.5429</v>
       </c>
       <c r="W2" t="n">
-        <v>2.2599</v>
+        <v>1.695</v>
       </c>
       <c r="X2" t="n">
         <v>-0.152</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>R. LOBACO MUÑOZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3367</v>
+        <v>5.493</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2918</v>
+        <v>3.9261</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0449</v>
+        <v>1.5669</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4977</v>
+        <v>-0.7262</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3716</v>
+        <v>-0.1461</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1261</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7258</v>
+        <v>-0.0511</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6244</v>
+        <v>0.4047</v>
       </c>
       <c r="L3" t="n">
-        <v>3.1014</v>
+        <v>-0.4558</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2281</v>
+        <v>-0.6751</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2528</v>
+        <v>-0.5508</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0247</v>
+        <v>-0.1243</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2175</v>
+        <v>2.8276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.4801</v>
+        <v>2.8276</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9215</v>
+        <v>1.2837</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8663999999999999</v>
+        <v>1.7172</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0551</v>
+        <v>-0.4335</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5429</v>
+        <v>2.1079</v>
       </c>
       <c r="W3" t="n">
-        <v>1.695</v>
+        <v>2.2599</v>
       </c>
       <c r="X3" t="n">
         <v>-0.152</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7178</v>
+        <v>3.5945</v>
       </c>
       <c r="E4" t="n">
         <v>1.7671</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9507</v>
+        <v>1.8274</v>
       </c>
       <c r="G4" t="n">
         <v>0.3387</v>
@@ -766,13 +766,13 @@
         <v>2.3926</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2038</v>
+        <v>0.0805</v>
       </c>
       <c r="T4" t="n">
         <v>0.1286</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0752</v>
+        <v>-0.0481</v>
       </c>
       <c r="V4" t="n">
         <v>0.7827</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5686</v>
+        <v>3.5293</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1114</v>
+        <v>4.477</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4573</v>
+        <v>-0.9477</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8195</v>
+        <v>2.6899</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8554</v>
+        <v>0.0244</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0359</v>
+        <v>2.6655</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4587</v>
+        <v>3.9587</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3057</v>
+        <v>0.9553</v>
       </c>
       <c r="L5" t="n">
-        <v>0.153</v>
+        <v>3.0034</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6392</v>
+        <v>-1.2688</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4504</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1889</v>
+        <v>-0.3379</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.87</v>
+        <v>2.1751</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3926</v>
+        <v>3.2626</v>
       </c>
       <c r="S5" t="n">
-        <v>2.576</v>
+        <v>0.3593</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5248</v>
+        <v>0.4759</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0512</v>
+        <v>-0.1166</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0432</v>
+        <v>-1.695</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3473</v>
+        <v>-2.8249</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3375</v>
+        <v>2.198</v>
       </c>
       <c r="E6" t="n">
-        <v>2.789</v>
+        <v>0.864</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5486</v>
+        <v>1.334</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7334000000000001</v>
+        <v>1.8195</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2219</v>
+        <v>1.8554</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5116000000000001</v>
+        <v>-0.0359</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2212</v>
+        <v>2.4587</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4562</v>
+        <v>2.3057</v>
       </c>
       <c r="L6" t="n">
-        <v>0.765</v>
+        <v>0.153</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4878</v>
+        <v>-0.6392</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2344</v>
+        <v>-0.4504</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2534</v>
+        <v>-0.1889</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1751</v>
+        <v>-0.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1751</v>
+        <v>2.3926</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4938</v>
+        <v>1.2053</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3073</v>
+        <v>1.2774</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1865</v>
+        <v>-0.0721</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.0647</v>
+        <v>0.0432</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7395</v>
+        <v>0.3904</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3252</v>
+        <v>-0.3473</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.879</v>
+        <v>2.0419</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0732</v>
+        <v>1.7399</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1942</v>
+        <v>0.302</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6899</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0244</v>
+        <v>0.2219</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6655</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9587</v>
+        <v>1.2212</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9553</v>
+        <v>0.4562</v>
       </c>
       <c r="L7" t="n">
-        <v>3.0034</v>
+        <v>0.765</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2688</v>
+        <v>-0.4878</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.2344</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3379</v>
+        <v>-0.2534</v>
       </c>
       <c r="P7" t="n">
         <v>2.1751</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.2626</v>
+        <v>2.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.291</v>
+        <v>1.1981</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0721</v>
+        <v>1.2582</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3632</v>
+        <v>-0.0601</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.695</v>
+        <v>-2.0647</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>-0.7395</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.8249</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.075</v>
+        <v>1.7774</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2769</v>
+        <v>2.0101</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2019</v>
+        <v>-0.2327</v>
       </c>
       <c r="G8" t="n">
         <v>1.2439</v>
@@ -1078,13 +1078,13 @@
         <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>0.656</v>
+        <v>0.3584</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4831</v>
+        <v>0.2163</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1729</v>
+        <v>0.1421</v>
       </c>
       <c r="V8" t="n">
         <v>-1.13</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7739</v>
+        <v>1.4871</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8427</v>
+        <v>1.3402</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0688</v>
+        <v>0.1469</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7509</v>
@@ -1156,13 +1156,13 @@
         <v>2.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2844</v>
+        <v>0.9977</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8411999999999999</v>
+        <v>1.3387</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5568</v>
+        <v>-0.341</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9347</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7078</v>
+        <v>-1.596</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7953</v>
+        <v>-0.6835</v>
       </c>
       <c r="F10" t="n">
         <v>-0.9125</v>
@@ -1234,10 +1234,10 @@
         <v>0.2175</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2175</v>
+        <v>-0.1057</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="U10" t="n">
         <v>-0.149</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. HERMANSON</t>
+          <t>M. TOWNES VILLAR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2321</v>
+        <v>-2.0928</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4717</v>
+        <v>-2.8905</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2396</v>
+        <v>0.7977</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0966</v>
+        <v>-2.6149</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1977</v>
+        <v>-0.6538</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.8989</v>
+        <v>-1.9611</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.1787</v>
+        <v>-1.7597</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0182</v>
+        <v>-0.1365</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.1969</v>
+        <v>-1.6232</v>
       </c>
       <c r="M11" t="n">
-        <v>0.082</v>
+        <v>-0.8552</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.216</v>
+        <v>-0.5173</v>
       </c>
       <c r="O11" t="n">
-        <v>0.298</v>
+        <v>-0.3379</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6525</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R11" t="n">
-        <v>0.435</v>
+        <v>2.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.483</v>
+        <v>0.4158</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2055</v>
+        <v>0.7859</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2775</v>
+        <v>-0.3701</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.1938</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.3459</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.152</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. TOWNES VILLAR</t>
+          <t>C. HERMANSON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4728</v>
+        <v>-3.0895</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.3938</v>
+        <v>-3.3599</v>
       </c>
       <c r="F12" t="n">
-        <v>0.921</v>
+        <v>0.2704</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.6149</v>
+        <v>-2.0966</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6538</v>
+        <v>-0.1977</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9611</v>
+        <v>-1.8989</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.7597</v>
+        <v>-2.1787</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1365</v>
+        <v>0.0182</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.6232</v>
+        <v>-2.1969</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8552</v>
+        <v>0.082</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5173</v>
+        <v>-0.216</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3379</v>
+        <v>0.298</v>
       </c>
       <c r="P12" t="n">
+        <v>-0.6525</v>
+      </c>
+      <c r="Q12" t="n">
         <v>-1.0875</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-3.2626</v>
-      </c>
       <c r="R12" t="n">
-        <v>2.1751</v>
+        <v>0.435</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-0.3404</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7174</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2468</v>
+        <v>-0.2466</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1938</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3459</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,31 +1423,31 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.1414</v>
+        <v>19.5113</v>
       </c>
       <c r="E13" t="n">
-        <v>10.8824</v>
+        <v>12.2524</v>
       </c>
       <c r="F13" t="n">
-        <v>7.259100000000002</v>
+        <v>7.259</v>
       </c>
       <c r="G13" t="n">
         <v>2.426700000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8173</v>
+        <v>3.817299999999999</v>
       </c>
       <c r="I13" t="n">
         <v>-1.3905</v>
       </c>
       <c r="J13" t="n">
-        <v>9.886699999999999</v>
+        <v>9.886699999999998</v>
       </c>
       <c r="K13" t="n">
-        <v>9.065799999999998</v>
+        <v>9.065799999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8209000000000002</v>
+        <v>0.8209000000000004</v>
       </c>
       <c r="M13" t="n">
         <v>-7.4601</v>
@@ -1468,22 +1468,22 @@
         <v>22.8383</v>
       </c>
       <c r="S13" t="n">
-        <v>4.9931</v>
+        <v>6.363</v>
       </c>
       <c r="T13" t="n">
-        <v>6.6816</v>
+        <v>8.051500000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.6886</v>
+        <v>-1.6884</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1539000000000006</v>
+        <v>-0.1539000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>6.2769</v>
+        <v>6.276900000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.430700000000001</v>
+        <v>-6.430699999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0369</v>
+        <v>3.3028</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4323</v>
+        <v>4.5441</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3954</v>
+        <v>-1.2413</v>
       </c>
       <c r="G14" t="n">
         <v>2.1072</v>
@@ -1546,13 +1546,13 @@
         <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1578</v>
+        <v>-0.892</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0721</v>
+        <v>0.1839</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2299</v>
+        <v>-1.0758</v>
       </c>
       <c r="V14" t="n">
         <v>0.5649999999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>G. MAIZA APECECHEA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.734</v>
+        <v>0.7028</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3784</v>
+        <v>2.2811</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6443</v>
+        <v>-1.5783</v>
       </c>
       <c r="G15" t="n">
-        <v>1.527</v>
+        <v>3.0846</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0865</v>
+        <v>1.4598</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5594</v>
+        <v>1.6248</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0173</v>
+        <v>2.9453</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6858</v>
+        <v>1.2806</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6686</v>
+        <v>1.6647</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4902</v>
+        <v>0.1393</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5994</v>
+        <v>0.1792</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1091</v>
+        <v>-0.0399</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.1751</v>
+        <v>0.2175</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.6976</v>
+        <v>-0.2175</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4027</v>
+        <v>-1.0996</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3638</v>
+        <v>-0.0769</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.961</v>
+        <v>-1.0227</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.0207</v>
+        <v>-1.4997</v>
       </c>
       <c r="W15" t="n">
-        <v>1.695</v>
+        <v>-0.3698</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7156</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. MAIZA APECECHEA</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0092</v>
+        <v>-0.1793</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2811</v>
+        <v>0.9255</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2719</v>
+        <v>-1.1048</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0846</v>
+        <v>1.527</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4598</v>
+        <v>2.0865</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6248</v>
+        <v>-0.5594</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9453</v>
+        <v>2.0173</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2806</v>
+        <v>2.6858</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6647</v>
+        <v>-0.6686</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1393</v>
+        <v>-0.4902</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1792</v>
+        <v>-0.5994</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0399</v>
+        <v>0.1091</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2175</v>
+        <v>-3.6976</v>
       </c>
       <c r="R16" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.7932</v>
+        <v>0.4894</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0769</v>
+        <v>0.9109</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.7163</v>
+        <v>-0.4215</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4997</v>
+        <v>-0.0207</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3698</v>
+        <v>1.695</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.13</v>
+        <v>-1.7156</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5021</v>
+        <v>-0.3209</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3195</v>
+        <v>-0.9843</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8175</v>
+        <v>0.6633</v>
       </c>
       <c r="G17" t="n">
         <v>1.1853</v>
@@ -1780,13 +1780,13 @@
         <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8802</v>
+        <v>1.0614</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3341</v>
+        <v>0.6694</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5462</v>
+        <v>0.392</v>
       </c>
       <c r="V17" t="n">
         <v>1.13</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. NICOLAU ALEDON</t>
+          <t>O. HANZLIK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1711</v>
+        <v>-1.2996</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6657</v>
+        <v>1.3261</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5054</v>
+        <v>-2.6257</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8489</v>
+        <v>-2.8155</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3923</v>
+        <v>-0.4959</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4566</v>
+        <v>-2.3196</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1393</v>
+        <v>-1.0614</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0246</v>
+        <v>0.7514</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1147</v>
+        <v>-1.8128</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9882</v>
+        <v>-1.7541</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4169</v>
+        <v>-1.2473</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5714</v>
+        <v>-0.5068</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0172</v>
+        <v>-0.6363</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1971</v>
+        <v>-0.2199</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2143</v>
+        <v>-0.4164</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.4997</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3904</v>
+        <v>2.8249</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3904</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. HANZLIK</t>
+          <t>M. MOTOS CABODEVILLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6021</v>
+        <v>-2.0902</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6556</v>
+        <v>-1.7041</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.2577</v>
+        <v>-0.3861</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8155</v>
+        <v>0.4815</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4959</v>
+        <v>-0.8699</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.3196</v>
+        <v>1.3514</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0614</v>
+        <v>0.3917</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7514</v>
+        <v>0.2769</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.8128</v>
+        <v>0.1147</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7541</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2473</v>
+        <v>-1.1468</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5068</v>
+        <v>1.2367</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6525</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="R19" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.9388</v>
+        <v>-0.7892</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8904</v>
+        <v>0.2968</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0484</v>
+        <v>-1.086</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4997</v>
+        <v>-1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>2.8249</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. MOTOS CABODEVILLA</t>
+          <t>J. NICOLAU ALEDON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8648</v>
+        <v>-2.1891</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2629</v>
+        <v>-1.8892</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6019</v>
+        <v>-0.2999</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4815</v>
+        <v>-0.8489</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8699</v>
+        <v>-0.3923</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3514</v>
+        <v>-0.4566</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3917</v>
+        <v>0.1393</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2769</v>
+        <v>0.0246</v>
       </c>
       <c r="L20" t="n">
         <v>0.1147</v>
       </c>
       <c r="M20" t="n">
-        <v>0.08989999999999999</v>
+        <v>-0.9882</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1468</v>
+        <v>-0.4169</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2367</v>
+        <v>-0.5714</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6525</v>
+        <v>-1.305</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.3926</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5638</v>
+        <v>-0.0352</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.262</v>
+        <v>-0.0264</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.3018</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. ANSORREGUI DEBA</t>
+          <t>I. ARROYO VARELA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6086</v>
+        <v>-3.8989</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4272</v>
+        <v>-3.3752</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1814</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.1324</v>
+        <v>-0.9094</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1563</v>
+        <v>0.2644</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9762</v>
+        <v>-1.1738</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5298</v>
+        <v>-0.5211</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.976</v>
+        <v>0.9307</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5538</v>
+        <v>-1.4519</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6027</v>
+        <v>-0.3882</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1803</v>
+        <v>-0.6663</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4224</v>
+        <v>0.2781</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.87</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1751</v>
+        <v>-2.6101</v>
       </c>
       <c r="R21" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5891</v>
+        <v>-0.8367</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2776</v>
+        <v>-0.2439</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3115</v>
+        <v>-0.5927</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1952</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. ARROYO VARELA</t>
+          <t>M. ANSORREGUI DEBA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6002</v>
+        <v>-4.0787</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5987</v>
+        <v>-3.6508</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0015</v>
+        <v>-0.428</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9094</v>
+        <v>-3.1324</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2644</v>
+        <v>-2.1563</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1738</v>
+        <v>-0.9762</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5211</v>
+        <v>-1.5298</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9307</v>
+        <v>-0.976</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4519</v>
+        <v>-0.5538</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3882</v>
+        <v>-1.6027</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6663</v>
+        <v>-1.1803</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2781</v>
+        <v>-0.4224</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9576</v>
+        <v>-0.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.6101</v>
+        <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5381</v>
+        <v>0.119</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4675</v>
+        <v>0.0541</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0706</v>
+        <v>0.0649</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1952</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.5726</v>
+        <v>-5.8551</v>
       </c>
       <c r="E23" t="n">
         <v>-4.7323</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8403</v>
+        <v>-1.1228</v>
       </c>
       <c r="G23" t="n">
         <v>-3.1062</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1437</v>
+        <v>-0.1388</v>
       </c>
       <c r="T23" t="n">
         <v>0.1406</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0031</v>
+        <v>-0.2794</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-18.1414</v>
+        <v>-15.9062</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.258900000000001</v>
+        <v>-7.2591</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.8823</v>
+        <v>-8.647300000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.426800000000001</v>
+        <v>-2.426799999999999</v>
       </c>
       <c r="H24" t="n">
         <v>-3.8172</v>
@@ -2308,7 +2308,7 @@
         <v>2.2113</v>
       </c>
       <c r="M24" t="n">
-        <v>-9.886800000000001</v>
+        <v>-9.886799999999999</v>
       </c>
       <c r="N24" t="n">
         <v>-9.065799999999999</v>
@@ -2326,16 +2326,16 @@
         <v>11.9628</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.993200000000001</v>
+        <v>-2.758</v>
       </c>
       <c r="T24" t="n">
-        <v>1.6885</v>
+        <v>1.6886</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.6815</v>
+        <v>-4.4463</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1538999999999998</v>
+        <v>0.1539</v>
       </c>
       <c r="W24" t="n">
         <v>6.4307</v>
